--- a/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlRepoPledgeSearch004.xlsx
+++ b/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlRepoPledgeSearch004.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>组合代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -28,35 +28,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>已质押券面(元)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可质押券面(元)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持仓券面(元)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>债券名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持仓券面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可质押券面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已质押券面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>剩余券面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主体评级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>债项评级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登记托管机构</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -64,28 +48,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -110,7 +84,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -122,9 +96,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -417,16 +388,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="1" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="6" max="6" width="14.5" customWidth="1"/>
+    <col min="7" max="7" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -437,28 +408,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
